--- a/Code/matrice.xlsx
+++ b/Code/matrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E169098D-430E-47BE-85B6-F3B1F6E86A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8A0A88-E082-4A0F-A02D-E1AC3C362A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
